--- a/src/test/java/utilities/Project_InputData.xlsx
+++ b/src/test/java/utilities/Project_InputData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2D1BEFA1-06F8-46E9-B6A6-CBC9CA5C2825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{244310AB-B987-4BA7-9921-0E5227110237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D047B9D7-C76C-4BD0-BA8D-6AE4F516532B}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{D047B9D7-C76C-4BD0-BA8D-6AE4F516532B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,17 +15,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -437,6 +426,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
